--- a/upload/pagamentorp2025.xlsx
+++ b/upload/pagamentorp2025.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q174"/>
+  <dimension ref="A1:Q173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12003,12 +12003,12 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>9430960</t>
+          <t>9430966</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>1304</t>
+          <t>2037</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -12018,12 +12018,12 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>PM PEDRAS DE MARIA DA CRUZ</t>
+          <t>PM SAO JOAO DO PARAISO</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>25.209.156/0001-08</t>
+          <t>24.791.154/0001-07</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr">
@@ -12078,7 +12078,7 @@
       </c>
       <c r="P134" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1843527.35</t>
         </is>
       </c>
       <c r="Q134" s="2" t="inlineStr">
@@ -12090,27 +12090,27 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>9430966</t>
+          <t>9445785</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>2037</t>
+          <t>3893</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>2024-07-04 00:00:00</t>
+          <t>2024-12-12 00:00:00</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>PM SAO JOAO DO PARAISO</t>
+          <t>PM SERRA DOS AIMORES</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>24.791.154/0001-07</t>
+          <t>18.398.966/0001-94</t>
         </is>
       </c>
       <c r="F135" s="2" t="inlineStr">
@@ -12165,7 +12165,7 @@
       </c>
       <c r="P135" s="2" t="inlineStr">
         <is>
-          <t>1843527.35</t>
+          <t>2750000</t>
         </is>
       </c>
       <c r="Q135" s="2" t="inlineStr">
@@ -12177,12 +12177,12 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>9445785</t>
+          <t>9445786</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>3893</t>
+          <t>3892</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -12252,7 +12252,7 @@
       </c>
       <c r="P136" s="2" t="inlineStr">
         <is>
-          <t>2750000</t>
+          <t>751583.43</t>
         </is>
       </c>
       <c r="Q136" s="2" t="inlineStr">
@@ -12264,12 +12264,12 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>9445786</t>
+          <t>9445788</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>3892</t>
+          <t>3894</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -12339,7 +12339,7 @@
       </c>
       <c r="P137" s="2" t="inlineStr">
         <is>
-          <t>751583.43</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="Q137" s="2" t="inlineStr">
@@ -12351,17 +12351,17 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>9445788</t>
+          <t>9445983</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>3894</t>
+          <t>4046</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>2024-12-12 00:00:00</t>
+          <t>2024-12-13 00:00:00</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
@@ -12426,7 +12426,7 @@
       </c>
       <c r="P138" s="2" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>920000</t>
         </is>
       </c>
       <c r="Q138" s="2" t="inlineStr">
@@ -12438,42 +12438,42 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>9445983</t>
+          <t>9446012</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>4046</t>
+          <t>87</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>2024-12-13 00:00:00</t>
+          <t>2024-12-16 00:00:00</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>PM SERRA DOS AIMORES</t>
+          <t>ASSOC. DE PROT. E ASSIST. AOS CONENADOS DE SANTA BARBARA</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>18.398.966/0001-94</t>
+          <t>05.134.204/0001-39</t>
         </is>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>SEE</t>
+          <t>SEJUSP</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1451</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE EDUCACAO</t>
+          <t>SECRETARIA DE ESTADO DE JUSTICA E SEGURANCA PUBLICA</t>
         </is>
       </c>
       <c r="I139" s="2" t="inlineStr">
@@ -12513,7 +12513,7 @@
       </c>
       <c r="P139" s="2" t="inlineStr">
         <is>
-          <t>920000</t>
+          <t>15000</t>
         </is>
       </c>
       <c r="Q139" s="2" t="inlineStr">
@@ -12525,42 +12525,42 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>9446012</t>
+          <t>9446033</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>1005</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>2024-12-16 00:00:00</t>
+          <t>2024-12-17 00:00:00</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>ASSOC. DE PROT. E ASSIST. AOS CONENADOS DE SANTA BARBARA</t>
+          <t>PM MATEUS LEME</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>05.134.204/0001-39</t>
+          <t>18.715.433/0001-99</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>SEJUSP</t>
+          <t>SEE</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>1451</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE JUSTICA E SEGURANCA PUBLICA</t>
+          <t>SECRETARIA DE ESTADO DE EDUCACAO</t>
         </is>
       </c>
       <c r="I140" s="2" t="inlineStr">
@@ -12600,7 +12600,7 @@
       </c>
       <c r="P140" s="2" t="inlineStr">
         <is>
-          <t>15000</t>
+          <t>711191.99</t>
         </is>
       </c>
       <c r="Q140" s="2" t="inlineStr">
@@ -12612,12 +12612,12 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>9446033</t>
+          <t>9446037</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>1005</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -12627,12 +12627,12 @@
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>PM MATEUS LEME</t>
+          <t>PM COMENDADOR GOMES</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>18.715.433/0001-99</t>
+          <t>18.449.173/0001-57</t>
         </is>
       </c>
       <c r="F141" s="2" t="inlineStr">
@@ -12687,7 +12687,7 @@
       </c>
       <c r="P141" s="2" t="inlineStr">
         <is>
-          <t>711191.99</t>
+          <t>249340.97</t>
         </is>
       </c>
       <c r="Q141" s="2" t="inlineStr">
@@ -12699,52 +12699,52 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>9446037</t>
+          <t>9447069</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>403</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>2024-12-17 00:00:00</t>
+          <t>2024-12-26 00:00:00</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>PM COMENDADOR GOMES</t>
+          <t>PM MATHIAS LOBATO</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>18.449.173/0001-57</t>
+          <t>18.332.619/0001-69</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>SEE</t>
+          <t>SEAPA</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1231</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE EDUCACAO</t>
+          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUARIA E ABASTECIMENTO</t>
         </is>
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>41</t>
         </is>
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>AUXILIOS</t>
+          <t>CONTRIBUICOES</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
@@ -12754,17 +12754,17 @@
       </c>
       <c r="L142" s="2" t="inlineStr">
         <is>
-          <t>AUXILIOS</t>
+          <t>CONTRIBUICOES</t>
         </is>
       </c>
       <c r="M142" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="N142" s="2" t="inlineStr">
         <is>
-          <t>RECURSOS ORDINARIOS - RECURSOS NAO VINCULADOS DE IMPOSTOS</t>
+          <t>RECURSOS ORDINARIOS - OUTROS RECURSOS NAO VINCULADOS</t>
         </is>
       </c>
       <c r="O142" s="2" t="inlineStr">
@@ -12774,7 +12774,7 @@
       </c>
       <c r="P142" s="2" t="inlineStr">
         <is>
-          <t>249340.97</t>
+          <t>1450000</t>
         </is>
       </c>
       <c r="Q142" s="2" t="inlineStr">
@@ -12786,12 +12786,12 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>9447069</t>
+          <t>9447071</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>403</t>
+          <t>404</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -12861,7 +12861,7 @@
       </c>
       <c r="P143" s="2" t="inlineStr">
         <is>
-          <t>1450000</t>
+          <t>2000000</t>
         </is>
       </c>
       <c r="Q143" s="2" t="inlineStr">
@@ -12873,52 +12873,52 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>9447071</t>
+          <t>9447083</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>89</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>2024-12-26 00:00:00</t>
+          <t>2024-12-19 00:00:00</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>PM MATHIAS LOBATO</t>
+          <t>ASSOC. DE PROT. E ASSIST. AO CONDENADO DE GOVERNADOR VALDARES</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>18.332.619/0001-69</t>
+          <t>07.828.198/0001-45</t>
         </is>
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>SEAPA</t>
+          <t>SEJUSP</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>1231</t>
+          <t>1451</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUARIA E ABASTECIMENTO</t>
+          <t>SECRETARIA DE ESTADO DE JUSTICA E SEGURANCA PUBLICA</t>
         </is>
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>42</t>
         </is>
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>CONTRIBUICOES</t>
+          <t>AUXILIOS</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
@@ -12928,17 +12928,17 @@
       </c>
       <c r="L144" s="2" t="inlineStr">
         <is>
-          <t>CONTRIBUICOES</t>
+          <t>AUXILIOS</t>
         </is>
       </c>
       <c r="M144" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N144" s="2" t="inlineStr">
         <is>
-          <t>RECURSOS ORDINARIOS - OUTROS RECURSOS NAO VINCULADOS</t>
+          <t>RECURSOS ORDINARIOS - RECURSOS NAO VINCULADOS DE IMPOSTOS</t>
         </is>
       </c>
       <c r="O144" s="2" t="inlineStr">
@@ -12948,7 +12948,7 @@
       </c>
       <c r="P144" s="2" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="Q144" s="2" t="inlineStr">
@@ -12960,42 +12960,42 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>9447083</t>
+          <t>9447275</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>1022</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>2024-12-19 00:00:00</t>
+          <t>2024-12-27 00:00:00</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>ASSOC. DE PROT. E ASSIST. AO CONDENADO DE GOVERNADOR VALDARES</t>
+          <t>PM GRAO MOGOL</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>07.828.198/0001-45</t>
+          <t>20.716.627/0001-50</t>
         </is>
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>SEJUSP</t>
+          <t>SEE</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>1451</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE JUSTICA E SEGURANCA PUBLICA</t>
+          <t>SECRETARIA DE ESTADO DE EDUCACAO</t>
         </is>
       </c>
       <c r="I145" s="2" t="inlineStr">
@@ -13035,7 +13035,7 @@
       </c>
       <c r="P145" s="2" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>774766.69</t>
         </is>
       </c>
       <c r="Q145" s="2" t="inlineStr">
@@ -13047,12 +13047,12 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>9447275</t>
+          <t>9447277</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>1019</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
@@ -13062,12 +13062,12 @@
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>PM GRAO MOGOL</t>
+          <t>PM SAO ROMAO</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>20.716.627/0001-50</t>
+          <t>24.891.418/0001-02</t>
         </is>
       </c>
       <c r="F146" s="2" t="inlineStr">
@@ -13122,7 +13122,7 @@
       </c>
       <c r="P146" s="2" t="inlineStr">
         <is>
-          <t>774766.69</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="Q146" s="2" t="inlineStr">
@@ -13134,12 +13134,12 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>9447277</t>
+          <t>9447278</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>1019</t>
+          <t>1021</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -13149,12 +13149,12 @@
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>PM SAO ROMAO</t>
+          <t>PM FREI GASPAR</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>24.891.418/0001-02</t>
+          <t>18.404.913/0001-39</t>
         </is>
       </c>
       <c r="F147" s="2" t="inlineStr">
@@ -13209,7 +13209,7 @@
       </c>
       <c r="P147" s="2" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>711191.99</t>
         </is>
       </c>
       <c r="Q147" s="2" t="inlineStr">
@@ -13221,12 +13221,12 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>9447278</t>
+          <t>9447279</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>1021</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -13236,12 +13236,12 @@
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>PM FREI GASPAR</t>
+          <t>PM CAREACU</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>18.404.913/0001-39</t>
+          <t>17.935.388/0001-15</t>
         </is>
       </c>
       <c r="F148" s="2" t="inlineStr">
@@ -13296,7 +13296,7 @@
       </c>
       <c r="P148" s="2" t="inlineStr">
         <is>
-          <t>711191.99</t>
+          <t>3012564.37</t>
         </is>
       </c>
       <c r="Q148" s="2" t="inlineStr">
@@ -13308,12 +13308,12 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>9447279</t>
+          <t>9447280</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>1016</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -13323,12 +13323,12 @@
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>PM CAREACU</t>
+          <t>PM BOCAINA DE MINAS</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>17.935.388/0001-15</t>
+          <t>18.194.076/0001-60</t>
         </is>
       </c>
       <c r="F149" s="2" t="inlineStr">
@@ -13383,7 +13383,7 @@
       </c>
       <c r="P149" s="2" t="inlineStr">
         <is>
-          <t>3012564.37</t>
+          <t>635127.6</t>
         </is>
       </c>
       <c r="Q149" s="2" t="inlineStr">
@@ -13395,12 +13395,12 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>9447280</t>
+          <t>9447282</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>1016</t>
+          <t>1017</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
@@ -13410,12 +13410,12 @@
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>PM BOCAINA DE MINAS</t>
+          <t>PM BRAS PIRES</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>18.194.076/0001-60</t>
+          <t>18.128.272/0001-37</t>
         </is>
       </c>
       <c r="F150" s="2" t="inlineStr">
@@ -13470,7 +13470,7 @@
       </c>
       <c r="P150" s="2" t="inlineStr">
         <is>
-          <t>635127.6</t>
+          <t>427000</t>
         </is>
       </c>
       <c r="Q150" s="2" t="inlineStr">
@@ -13482,12 +13482,12 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>9447282</t>
+          <t>9447283</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>1017</t>
+          <t>1018</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
@@ -13497,12 +13497,12 @@
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>PM BRAS PIRES</t>
+          <t>PM BELMIRO BRAGA</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>18.128.272/0001-37</t>
+          <t>18.338.129/0001-70</t>
         </is>
       </c>
       <c r="F151" s="2" t="inlineStr">
@@ -13557,7 +13557,7 @@
       </c>
       <c r="P151" s="2" t="inlineStr">
         <is>
-          <t>427000</t>
+          <t>556800</t>
         </is>
       </c>
       <c r="Q151" s="2" t="inlineStr">
@@ -13569,12 +13569,12 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>9447283</t>
+          <t>9447284</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>1018</t>
+          <t>1020</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
@@ -13584,12 +13584,12 @@
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>PM BELMIRO BRAGA</t>
+          <t>PM BOM JARDIM DE MINAS</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>18.338.129/0001-70</t>
+          <t>18.684.217/0001-23</t>
         </is>
       </c>
       <c r="F152" s="2" t="inlineStr">
@@ -13644,7 +13644,7 @@
       </c>
       <c r="P152" s="2" t="inlineStr">
         <is>
-          <t>556800</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="Q152" s="2" t="inlineStr">
@@ -13656,12 +13656,12 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>9447284</t>
+          <t>9447285</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>396</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
@@ -13671,12 +13671,12 @@
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>PM BOM JARDIM DE MINAS</t>
+          <t>ASSOCIACAO EFA OESTE DO MUCURI</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>18.684.217/0001-23</t>
+          <t>11.211.251/0001-31</t>
         </is>
       </c>
       <c r="F153" s="2" t="inlineStr">
@@ -13696,12 +13696,12 @@
       </c>
       <c r="I153" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>43</t>
         </is>
       </c>
       <c r="J153" s="2" t="inlineStr">
         <is>
-          <t>AUXILIOS</t>
+          <t>SUBVENCOES SOCIAIS</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr">
@@ -13711,17 +13711,17 @@
       </c>
       <c r="L153" s="2" t="inlineStr">
         <is>
-          <t>AUXILIOS</t>
+          <t>SUBVENCOES SOCIAIS</t>
         </is>
       </c>
       <c r="M153" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>21</t>
         </is>
       </c>
       <c r="N153" s="2" t="inlineStr">
         <is>
-          <t>RECURSOS ORDINARIOS - RECURSOS NAO VINCULADOS DE IMPOSTOS</t>
+          <t>COTA ESTADUAL DO SALARIO EDUCACAO - QESE</t>
         </is>
       </c>
       <c r="O153" s="2" t="inlineStr">
@@ -13731,7 +13731,7 @@
       </c>
       <c r="P153" s="2" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>62400</t>
         </is>
       </c>
       <c r="Q153" s="2" t="inlineStr">
@@ -13743,52 +13743,52 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>9447285</t>
+          <t>9447290</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>2024-12-27 00:00:00</t>
+          <t>2024-12-26 00:00:00</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>ASSOCIACAO EFA OESTE DO MUCURI</t>
+          <t>PM RIO PARDO DE MINAS</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>11.211.251/0001-31</t>
+          <t>24.212.862/0001-46</t>
         </is>
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>SEE</t>
+          <t>SEDESE</t>
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1481</t>
         </is>
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE EDUCACAO</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL</t>
         </is>
       </c>
       <c r="I154" s="2" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>42</t>
         </is>
       </c>
       <c r="J154" s="2" t="inlineStr">
         <is>
-          <t>SUBVENCOES SOCIAIS</t>
+          <t>AUXILIOS</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
@@ -13798,17 +13798,17 @@
       </c>
       <c r="L154" s="2" t="inlineStr">
         <is>
-          <t>SUBVENCOES SOCIAIS</t>
+          <t>AUXILIOS</t>
         </is>
       </c>
       <c r="M154" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>15</t>
         </is>
       </c>
       <c r="N154" s="2" t="inlineStr">
         <is>
-          <t>COTA ESTADUAL DO SALARIO EDUCACAO - QESE</t>
+          <t>RECURSOS ORDINARIOS - OUTROS RECURSOS NAO VINCULADOS</t>
         </is>
       </c>
       <c r="O154" s="2" t="inlineStr">
@@ -13818,7 +13818,7 @@
       </c>
       <c r="P154" s="2" t="inlineStr">
         <is>
-          <t>62400</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="Q154" s="2" t="inlineStr">
@@ -13830,12 +13830,12 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>9447290</t>
+          <t>9447295</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
@@ -13845,12 +13845,12 @@
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>PM RIO PARDO DE MINAS</t>
+          <t>PM CATAGUASES</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>24.212.862/0001-46</t>
+          <t>17.702.499/0001-81</t>
         </is>
       </c>
       <c r="F155" s="2" t="inlineStr">
@@ -13905,7 +13905,7 @@
       </c>
       <c r="P155" s="2" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q155" s="2" t="inlineStr">
@@ -13917,42 +13917,42 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>9447295</t>
+          <t>9447296</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>3935</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>2024-12-26 00:00:00</t>
+          <t>2024-12-27 00:00:00</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>PM CATAGUASES</t>
+          <t>PM CARLOS CHAGAS</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>17.702.499/0001-81</t>
+          <t>18.477.315/0001-90</t>
         </is>
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t>SEDESE</t>
+          <t>SEGOV</t>
         </is>
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>1481</t>
+          <t>1491</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL</t>
+          <t>SECRETARIA DE ESTADO DE GOVERNO</t>
         </is>
       </c>
       <c r="I156" s="2" t="inlineStr">
@@ -13992,7 +13992,7 @@
       </c>
       <c r="P156" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="Q156" s="2" t="inlineStr">
@@ -14004,12 +14004,12 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>9447296</t>
+          <t>9447303</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>3935</t>
+          <t>417</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
@@ -14019,37 +14019,37 @@
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>PM CARLOS CHAGAS</t>
+          <t>PM BURITIZEIRO</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>18.477.315/0001-90</t>
+          <t>18.279.067/0001-72</t>
         </is>
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
-          <t>SEGOV</t>
+          <t>SEAPA</t>
         </is>
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>1491</t>
+          <t>1231</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE GOVERNO</t>
+          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUARIA E ABASTECIMENTO</t>
         </is>
       </c>
       <c r="I157" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>41</t>
         </is>
       </c>
       <c r="J157" s="2" t="inlineStr">
         <is>
-          <t>AUXILIOS</t>
+          <t>CONTRIBUICOES</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr">
@@ -14059,17 +14059,17 @@
       </c>
       <c r="L157" s="2" t="inlineStr">
         <is>
-          <t>AUXILIOS</t>
+          <t>CONTRIBUICOES</t>
         </is>
       </c>
       <c r="M157" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N157" s="2" t="inlineStr">
         <is>
-          <t>RECURSOS ORDINARIOS - OUTROS RECURSOS NAO VINCULADOS</t>
+          <t>RECURSOS ORDINARIOS - RECURSOS NAO VINCULADOS DE IMPOSTOS</t>
         </is>
       </c>
       <c r="O157" s="2" t="inlineStr">
@@ -14079,7 +14079,7 @@
       </c>
       <c r="P157" s="2" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q157" s="2" t="inlineStr">
@@ -14091,52 +14091,52 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>9447303</t>
+          <t>9447316</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>417</t>
+          <t>55</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>2024-12-27 00:00:00</t>
+          <t>2024-12-26 00:00:00</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>PM BURITIZEIRO</t>
+          <t>APJ APRENDER PRODUZIR JUNTOS</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>18.279.067/0001-72</t>
+          <t>22.057.335/0001-89</t>
         </is>
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>SEAPA</t>
+          <t>SEDESE</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>1231</t>
+          <t>1481</t>
         </is>
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUARIA E ABASTECIMENTO</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL</t>
         </is>
       </c>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>43</t>
         </is>
       </c>
       <c r="J158" s="2" t="inlineStr">
         <is>
-          <t>CONTRIBUICOES</t>
+          <t>SUBVENCOES SOCIAIS</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
@@ -14146,17 +14146,17 @@
       </c>
       <c r="L158" s="2" t="inlineStr">
         <is>
-          <t>CONTRIBUICOES</t>
+          <t>SUBVENCOES SOCIAIS</t>
         </is>
       </c>
       <c r="M158" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>71</t>
         </is>
       </c>
       <c r="N158" s="2" t="inlineStr">
         <is>
-          <t>RECURSOS ORDINARIOS - RECURSOS NAO VINCULADOS DE IMPOSTOS</t>
+          <t>RECURSOS DO FUNDO ESTADUAL DE ERRADICACAO DA MISERIA</t>
         </is>
       </c>
       <c r="O158" s="2" t="inlineStr">
@@ -14166,7 +14166,7 @@
       </c>
       <c r="P158" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3910342</t>
         </is>
       </c>
       <c r="Q158" s="2" t="inlineStr">
@@ -14178,52 +14178,52 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>9447316</t>
+          <t>9447368</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>3934</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>2024-12-26 00:00:00</t>
+          <t>2024-12-27 00:00:00</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>APJ APRENDER PRODUZIR JUNTOS</t>
+          <t>PM ESPINOSA</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>22.057.335/0001-89</t>
+          <t>18.650.952/0001-16</t>
         </is>
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
-          <t>SEDESE</t>
+          <t>SEGOV</t>
         </is>
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>1481</t>
+          <t>1491</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL</t>
+          <t>SECRETARIA DE ESTADO DE GOVERNO</t>
         </is>
       </c>
       <c r="I159" s="2" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>42</t>
         </is>
       </c>
       <c r="J159" s="2" t="inlineStr">
         <is>
-          <t>SUBVENCOES SOCIAIS</t>
+          <t>AUXILIOS</t>
         </is>
       </c>
       <c r="K159" s="2" t="inlineStr">
@@ -14233,44 +14233,44 @@
       </c>
       <c r="L159" s="2" t="inlineStr">
         <is>
-          <t>SUBVENCOES SOCIAIS</t>
+          <t>AUXILIOS</t>
         </is>
       </c>
       <c r="M159" s="2" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>15</t>
         </is>
       </c>
       <c r="N159" s="2" t="inlineStr">
         <is>
-          <t>RECURSOS DO FUNDO ESTADUAL DE ERRADICACAO DA MISERIA</t>
+          <t>RECURSOS ORDINARIOS - OUTROS RECURSOS NAO VINCULADOS</t>
         </is>
       </c>
       <c r="O159" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>390725.92</t>
         </is>
       </c>
       <c r="P159" s="2" t="inlineStr">
         <is>
-          <t>3910342</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q159" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>390725.92</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>9447368</t>
+          <t>9447369</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>3934</t>
+          <t>5177</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
@@ -14280,27 +14280,27 @@
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>PM ESPINOSA</t>
+          <t>PM SERRA DOS AIMORES</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>18.650.952/0001-16</t>
+          <t>18.398.966/0001-94</t>
         </is>
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
-          <t>SEGOV</t>
+          <t>SEE</t>
         </is>
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>1491</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE GOVERNO</t>
+          <t>SECRETARIA DE ESTADO DE EDUCACAO</t>
         </is>
       </c>
       <c r="I160" s="2" t="inlineStr">
@@ -14325,39 +14325,39 @@
       </c>
       <c r="M160" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N160" s="2" t="inlineStr">
         <is>
-          <t>RECURSOS ORDINARIOS - OUTROS RECURSOS NAO VINCULADOS</t>
+          <t>RECURSOS ORDINARIOS - RECURSOS NAO VINCULADOS DE IMPOSTOS</t>
         </is>
       </c>
       <c r="O160" s="2" t="inlineStr">
         <is>
-          <t>390725.92</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P160" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>430000</t>
         </is>
       </c>
       <c r="Q160" s="2" t="inlineStr">
         <is>
-          <t>390725.92</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>9447369</t>
+          <t>9447370</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>5177</t>
+          <t>4406</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -14367,12 +14367,12 @@
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>PM SERRA DOS AIMORES</t>
+          <t>PM PINTOPOLIS</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>18.398.966/0001-94</t>
+          <t>01.612.481/0001-59</t>
         </is>
       </c>
       <c r="F161" s="2" t="inlineStr">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="P161" s="2" t="inlineStr">
         <is>
-          <t>430000</t>
+          <t>2007154.98</t>
         </is>
       </c>
       <c r="Q161" s="2" t="inlineStr">
@@ -14439,12 +14439,12 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>9447370</t>
+          <t>9447377</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>4406</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
@@ -14454,12 +14454,12 @@
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>PM PINTOPOLIS</t>
+          <t>PM SANTO ANTONIO DO MONTE</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>01.612.481/0001-59</t>
+          <t>16.870.974/0001-66</t>
         </is>
       </c>
       <c r="F162" s="2" t="inlineStr">
@@ -14509,69 +14509,69 @@
       </c>
       <c r="O162" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="P162" s="2" t="inlineStr">
         <is>
-          <t>2007154.98</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q162" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>9447377</t>
+          <t>9447443</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>3457</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>2024-12-27 00:00:00</t>
+          <t>2024-12-30 00:00:00</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>PM SANTO ANTONIO DO MONTE</t>
+          <t>ASSOCIACAO CORAL FLOR DA TERRA</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>16.870.974/0001-66</t>
+          <t>21.785.039/0001-31</t>
         </is>
       </c>
       <c r="F163" s="2" t="inlineStr">
         <is>
-          <t>SEE</t>
+          <t>SECULT</t>
         </is>
       </c>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="H163" s="2" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE EDUCACAO</t>
+          <t>SECRETARIA DE ESTADO DE CULTURA E TURISMO</t>
         </is>
       </c>
       <c r="I163" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>41</t>
         </is>
       </c>
       <c r="J163" s="2" t="inlineStr">
         <is>
-          <t>AUXILIOS</t>
+          <t>CONTRIBUICOES</t>
         </is>
       </c>
       <c r="K163" s="2" t="inlineStr">
@@ -14581,7 +14581,7 @@
       </c>
       <c r="L163" s="2" t="inlineStr">
         <is>
-          <t>AUXILIOS</t>
+          <t>CONTRIBUICOES</t>
         </is>
       </c>
       <c r="M163" s="2" t="inlineStr">
@@ -14596,7 +14596,7 @@
       </c>
       <c r="O163" s="2" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="P163" s="2" t="inlineStr">
@@ -14606,19 +14606,19 @@
       </c>
       <c r="Q163" s="2" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>9447443</t>
+          <t>9447445</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>3457</t>
+          <t>3936</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
@@ -14628,37 +14628,37 @@
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>ASSOCIACAO CORAL FLOR DA TERRA</t>
+          <t>PM SAO JOAQUIM DE BICAS</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>21.785.039/0001-31</t>
+          <t>01.612.516/0001-50</t>
         </is>
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
-          <t>SECULT</t>
+          <t>SEGOV</t>
         </is>
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1491</t>
         </is>
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE CULTURA E TURISMO</t>
+          <t>SECRETARIA DE ESTADO DE GOVERNO</t>
         </is>
       </c>
       <c r="I164" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>42</t>
         </is>
       </c>
       <c r="J164" s="2" t="inlineStr">
         <is>
-          <t>CONTRIBUICOES</t>
+          <t>AUXILIOS</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
@@ -14668,22 +14668,22 @@
       </c>
       <c r="L164" s="2" t="inlineStr">
         <is>
-          <t>CONTRIBUICOES</t>
+          <t>AUXILIOS</t>
         </is>
       </c>
       <c r="M164" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="N164" s="2" t="inlineStr">
         <is>
-          <t>RECURSOS ORDINARIOS - RECURSOS NAO VINCULADOS DE IMPOSTOS</t>
+          <t>RECURSOS ORDINARIOS - OUTROS RECURSOS NAO VINCULADOS</t>
         </is>
       </c>
       <c r="O164" s="2" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>1761036.8</t>
         </is>
       </c>
       <c r="P164" s="2" t="inlineStr">
@@ -14693,19 +14693,19 @@
       </c>
       <c r="Q164" s="2" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>1761036.8</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>9447445</t>
+          <t>9447447</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>3936</t>
+          <t>3937</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -14715,12 +14715,12 @@
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>PM SAO JOAQUIM DE BICAS</t>
+          <t>PM SAO JOSE DA SAFIRA</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>01.612.516/0001-50</t>
+          <t>18.409.235/0001-05</t>
         </is>
       </c>
       <c r="F165" s="2" t="inlineStr">
@@ -14770,7 +14770,7 @@
       </c>
       <c r="O165" s="2" t="inlineStr">
         <is>
-          <t>1761036.8</t>
+          <t>1050000</t>
         </is>
       </c>
       <c r="P165" s="2" t="inlineStr">
@@ -14780,19 +14780,19 @@
       </c>
       <c r="Q165" s="2" t="inlineStr">
         <is>
-          <t>1761036.8</t>
+          <t>1050000</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>9447447</t>
+          <t>9447451</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>3937</t>
+          <t>888</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
@@ -14802,27 +14802,27 @@
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>PM SAO JOSE DA SAFIRA</t>
+          <t>PM DIVINOPOLIS</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>18.409.235/0001-05</t>
+          <t>18.291.351/0001-64</t>
         </is>
       </c>
       <c r="F166" s="2" t="inlineStr">
         <is>
-          <t>SEGOV</t>
+          <t>SEINFRA</t>
         </is>
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>1491</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE GOVERNO</t>
+          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIAS</t>
         </is>
       </c>
       <c r="I166" s="2" t="inlineStr">
@@ -14847,39 +14847,39 @@
       </c>
       <c r="M166" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N166" s="2" t="inlineStr">
         <is>
-          <t>RECURSOS ORDINARIOS - OUTROS RECURSOS NAO VINCULADOS</t>
+          <t>RECURSOS ORDINARIOS - RECURSOS NAO VINCULADOS DE IMPOSTOS</t>
         </is>
       </c>
       <c r="O166" s="2" t="inlineStr">
         <is>
-          <t>1050000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P166" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1974495.62</t>
         </is>
       </c>
       <c r="Q166" s="2" t="inlineStr">
         <is>
-          <t>1050000</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>9447451</t>
+          <t>9447453</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>5725</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -14889,37 +14889,37 @@
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>PM DIVINOPOLIS</t>
+          <t>IRMANDADE DE NOSSA SENHORA DA SAUDE</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>18.291.351/0001-64</t>
+          <t>20.081.238/0001-04</t>
         </is>
       </c>
       <c r="F167" s="2" t="inlineStr">
         <is>
-          <t>SEINFRA</t>
+          <t>FES</t>
         </is>
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>4291</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIAS</t>
+          <t>FUNDO ESTADUAL DE SAUDE</t>
         </is>
       </c>
       <c r="I167" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>41</t>
         </is>
       </c>
       <c r="J167" s="2" t="inlineStr">
         <is>
-          <t>AUXILIOS</t>
+          <t>CONTRIBUICOES</t>
         </is>
       </c>
       <c r="K167" s="2" t="inlineStr">
@@ -14929,7 +14929,7 @@
       </c>
       <c r="L167" s="2" t="inlineStr">
         <is>
-          <t>AUXILIOS</t>
+          <t>CONTRIBUICOES</t>
         </is>
       </c>
       <c r="M167" s="2" t="inlineStr">
@@ -14944,29 +14944,29 @@
       </c>
       <c r="O167" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>998700</t>
         </is>
       </c>
       <c r="P167" s="2" t="inlineStr">
         <is>
-          <t>1974495.62</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q167" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>998700</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>9447453</t>
+          <t>9447454</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>5725</t>
+          <t>549</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
@@ -14976,27 +14976,27 @@
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>IRMANDADE DE NOSSA SENHORA DA SAUDE</t>
+          <t>PM LONTRA</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>20.081.238/0001-04</t>
+          <t>25.223.009/0001-92</t>
         </is>
       </c>
       <c r="F168" s="2" t="inlineStr">
         <is>
-          <t>FES</t>
+          <t>SEDESE</t>
         </is>
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>4291</t>
+          <t>1481</t>
         </is>
       </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE SAUDE</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL</t>
         </is>
       </c>
       <c r="I168" s="2" t="inlineStr">
@@ -15031,29 +15031,29 @@
       </c>
       <c r="O168" s="2" t="inlineStr">
         <is>
-          <t>998700</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P168" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>247000</t>
         </is>
       </c>
       <c r="Q168" s="2" t="inlineStr">
         <is>
-          <t>998700</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>9447454</t>
+          <t>9447461</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>398</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
@@ -15063,37 +15063,37 @@
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>PM LONTRA</t>
+          <t>ASSOCIACAO ESCOLA FAMILIA AGRICOLA DE COMERCINHO</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>25.223.009/0001-92</t>
+          <t>22.692.198/0001-54</t>
         </is>
       </c>
       <c r="F169" s="2" t="inlineStr">
         <is>
-          <t>SEDESE</t>
+          <t>SEE</t>
         </is>
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>1481</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="H169" s="2" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL</t>
+          <t>SECRETARIA DE ESTADO DE EDUCACAO</t>
         </is>
       </c>
       <c r="I169" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>43</t>
         </is>
       </c>
       <c r="J169" s="2" t="inlineStr">
         <is>
-          <t>CONTRIBUICOES</t>
+          <t>SUBVENCOES SOCIAIS</t>
         </is>
       </c>
       <c r="K169" s="2" t="inlineStr">
@@ -15103,17 +15103,17 @@
       </c>
       <c r="L169" s="2" t="inlineStr">
         <is>
-          <t>CONTRIBUICOES</t>
+          <t>SUBVENCOES SOCIAIS</t>
         </is>
       </c>
       <c r="M169" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>21</t>
         </is>
       </c>
       <c r="N169" s="2" t="inlineStr">
         <is>
-          <t>RECURSOS ORDINARIOS - RECURSOS NAO VINCULADOS DE IMPOSTOS</t>
+          <t>COTA ESTADUAL DO SALARIO EDUCACAO - QESE</t>
         </is>
       </c>
       <c r="O169" s="2" t="inlineStr">
@@ -15123,7 +15123,7 @@
       </c>
       <c r="P169" s="2" t="inlineStr">
         <is>
-          <t>247000</t>
+          <t>13776</t>
         </is>
       </c>
       <c r="Q169" s="2" t="inlineStr">
@@ -15135,12 +15135,12 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>9447461</t>
+          <t>9447488</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>398</t>
+          <t>890</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
@@ -15150,37 +15150,37 @@
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>ASSOCIACAO ESCOLA FAMILIA AGRICOLA DE COMERCINHO</t>
+          <t>PM TIMOTEO</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>22.692.198/0001-54</t>
+          <t>19.875.020/0001-34</t>
         </is>
       </c>
       <c r="F170" s="2" t="inlineStr">
         <is>
-          <t>SEE</t>
+          <t>SEINFRA</t>
         </is>
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE EDUCACAO</t>
+          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIAS</t>
         </is>
       </c>
       <c r="I170" s="2" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>42</t>
         </is>
       </c>
       <c r="J170" s="2" t="inlineStr">
         <is>
-          <t>SUBVENCOES SOCIAIS</t>
+          <t>AUXILIOS</t>
         </is>
       </c>
       <c r="K170" s="2" t="inlineStr">
@@ -15190,17 +15190,17 @@
       </c>
       <c r="L170" s="2" t="inlineStr">
         <is>
-          <t>SUBVENCOES SOCIAIS</t>
+          <t>AUXILIOS</t>
         </is>
       </c>
       <c r="M170" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>32</t>
         </is>
       </c>
       <c r="N170" s="2" t="inlineStr">
         <is>
-          <t>COTA ESTADUAL DO SALARIO EDUCACAO - QESE</t>
+          <t>EXPLORACAO DE RECURSOS MINERAIS</t>
         </is>
       </c>
       <c r="O170" s="2" t="inlineStr">
@@ -15210,7 +15210,7 @@
       </c>
       <c r="P170" s="2" t="inlineStr">
         <is>
-          <t>13776</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="Q170" s="2" t="inlineStr">
@@ -15222,12 +15222,12 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>9447488</t>
+          <t>9447490</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>890</t>
+          <t>889</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
@@ -15237,12 +15237,12 @@
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>PM TIMOTEO</t>
+          <t>PM ARAXA</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>19.875.020/0001-34</t>
+          <t>18.140.756/0001-00</t>
         </is>
       </c>
       <c r="F171" s="2" t="inlineStr">
@@ -15297,7 +15297,7 @@
       </c>
       <c r="P171" s="2" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>6884195.04</t>
         </is>
       </c>
       <c r="Q171" s="2" t="inlineStr">
@@ -15309,42 +15309,42 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>9447490</t>
+          <t>9447491</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>889</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>2024-12-30 00:00:00</t>
+          <t>2024-12-31 00:00:00</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>PM ARAXA</t>
+          <t>ASSOC.PESSOAS PORT.DEFICIENCIA DE MONTES CLAROS.</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>18.140.756/0001-00</t>
+          <t>21.373.873/0001-10</t>
         </is>
       </c>
       <c r="F172" s="2" t="inlineStr">
         <is>
-          <t>SEINFRA</t>
+          <t>SEDESE</t>
         </is>
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>1481</t>
         </is>
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIAS</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL</t>
         </is>
       </c>
       <c r="I172" s="2" t="inlineStr">
@@ -15369,39 +15369,39 @@
       </c>
       <c r="M172" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N172" s="2" t="inlineStr">
         <is>
-          <t>EXPLORACAO DE RECURSOS MINERAIS</t>
+          <t>RECURSOS ORDINARIOS - RECURSOS NAO VINCULADOS DE IMPOSTOS</t>
         </is>
       </c>
       <c r="O172" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>234952.38</t>
         </is>
       </c>
       <c r="P172" s="2" t="inlineStr">
         <is>
-          <t>6884195.04</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q172" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>234952.38</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>9447491</t>
+          <t>9447497</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>552</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
@@ -15411,12 +15411,12 @@
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>ASSOC.PESSOAS PORT.DEFICIENCIA DE MONTES CLAROS.</t>
+          <t>PM OLIVEIRA</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>21.373.873/0001-10</t>
+          <t>16.854.531/0001-81</t>
         </is>
       </c>
       <c r="F173" s="2" t="inlineStr">
@@ -15456,112 +15456,25 @@
       </c>
       <c r="M173" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>38</t>
         </is>
       </c>
       <c r="N173" s="2" t="inlineStr">
         <is>
-          <t>RECURSOS ORDINARIOS - RECURSOS NAO VINCULADOS DE IMPOSTOS</t>
+          <t>TRANSFERENCIAS DA UNIAO VINCULADAS AO ESPORTE</t>
         </is>
       </c>
       <c r="O173" s="2" t="inlineStr">
         <is>
-          <t>234952.38</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P173" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="Q173" s="2" t="inlineStr">
-        <is>
-          <t>234952.38</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" s="2" t="inlineStr">
-        <is>
-          <t>9447497</t>
-        </is>
-      </c>
-      <c r="B174" s="2" t="inlineStr">
-        <is>
-          <t>552</t>
-        </is>
-      </c>
-      <c r="C174" s="2" t="inlineStr">
-        <is>
-          <t>2024-12-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="D174" s="2" t="inlineStr">
-        <is>
-          <t>PM OLIVEIRA</t>
-        </is>
-      </c>
-      <c r="E174" s="2" t="inlineStr">
-        <is>
-          <t>16.854.531/0001-81</t>
-        </is>
-      </c>
-      <c r="F174" s="2" t="inlineStr">
-        <is>
-          <t>SEDESE</t>
-        </is>
-      </c>
-      <c r="G174" s="2" t="inlineStr">
-        <is>
-          <t>1481</t>
-        </is>
-      </c>
-      <c r="H174" s="2" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL</t>
-        </is>
-      </c>
-      <c r="I174" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="J174" s="2" t="inlineStr">
-        <is>
-          <t>AUXILIOS</t>
-        </is>
-      </c>
-      <c r="K174" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L174" s="2" t="inlineStr">
-        <is>
-          <t>AUXILIOS</t>
-        </is>
-      </c>
-      <c r="M174" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="N174" s="2" t="inlineStr">
-        <is>
-          <t>TRANSFERENCIAS DA UNIAO VINCULADAS AO ESPORTE</t>
-        </is>
-      </c>
-      <c r="O174" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P174" s="2" t="inlineStr">
-        <is>
-          <t>250000</t>
-        </is>
-      </c>
-      <c r="Q174" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
